--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B00A59-5097-4757-9217-72C42C61D2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3CDCB7-BE2E-4ACA-815F-06DA0BC68EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26325" yWindow="945" windowWidth="24750" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -1091,18 +1091,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="O23" s="1">
         <v>20</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>1500</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D3CDCB7-BE2E-4ACA-815F-06DA0BC68EEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82247621-9E90-467B-9954-502750AA6823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -884,18 +884,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="O14" s="1">
         <v>20</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>2256</v>
+        <v>2292</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>45120</v>
+        <v>45840</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -975,18 +975,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="O18" s="1">
         <v>20</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>511</v>
+        <v>529</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>10220</v>
+        <v>10580</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1003,18 +1003,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>389</v>
+        <v>417</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1016</v>
+        <v>1044</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>20320</v>
+        <v>20880</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1113,18 +1113,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>325</v>
+        <v>357</v>
       </c>
       <c r="O24" s="1">
         <v>20</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="0"/>
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>7060</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82247621-9E90-467B-9954-502750AA6823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CEF8AF-3A73-44A7-BAD6-C8416D64BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-21195" yWindow="915" windowWidth="17550" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -975,18 +975,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="O18" s="1">
         <v>20</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>10580</v>
+        <v>10520</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1091,18 +1091,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="O23" s="1">
         <v>20</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" si="0"/>
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>1620</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7CEF8AF-3A73-44A7-BAD6-C8416D64BA08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA7BCC1-D5B8-4D66-B5AC-7A88531A30D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-21195" yWindow="915" windowWidth="17550" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,7 +144,7 @@
     <t>26007 - OBRA HELENA Y JACOBO</t>
   </si>
   <si>
-    <t>26008 - OBRA ALBERTO Y EVA(SAN VICENTE)</t>
+    <t>26008 - OBRA ALBERTO Y EVA - C/ RIO SEGURA, 4. SAN VICENTE DEL RASPEIG</t>
   </si>
   <si>
     <t>24008 - OBRA C/HUERTO CAPUCHINOS, MURCIA</t>
@@ -195,11 +195,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1105,8 +1108,8 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+    <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>36</v>
       </c>
       <c r="I24" s="2">
@@ -1187,6 +1190,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA7BCC1-D5B8-4D66-B5AC-7A88531A30D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D2DAFF-BC66-4A68-B969-296EFF0B4932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-21195" yWindow="915" windowWidth="17550" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D2DAFF-BC66-4A68-B969-296EFF0B4932}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C691C2-F34A-46C9-8D7B-3C8834C82F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -713,18 +713,18 @@
         <v>284</v>
       </c>
       <c r="J8" s="2">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="O8" s="1">
         <v>20</v>
       </c>
       <c r="P8" s="1">
         <f t="shared" si="0"/>
-        <v>4083</v>
+        <v>4119</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="1"/>
-        <v>81660</v>
+        <v>82380</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -978,18 +978,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="O18" s="1">
         <v>20</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>526</v>
+        <v>554</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>10520</v>
+        <v>11080</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1006,18 +1006,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>417</v>
+        <v>441</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1044</v>
+        <v>1068</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>20880</v>
+        <v>21360</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1116,18 +1116,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>357</v>
+        <v>389</v>
       </c>
       <c r="O24" s="1">
         <v>20</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="0"/>
-        <v>385</v>
+        <v>417</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>7700</v>
+        <v>8340</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C691C2-F34A-46C9-8D7B-3C8834C82F76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32C2C07-0CA8-41FD-B855-7084746D577B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -887,18 +887,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>329</v>
+        <v>369</v>
       </c>
       <c r="O14" s="1">
         <v>20</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>2292</v>
+        <v>2332</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>45840</v>
+        <v>46640</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -978,18 +978,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>105</v>
+        <v>133</v>
       </c>
       <c r="O18" s="1">
         <v>20</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>554</v>
+        <v>582</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>11080</v>
+        <v>11640</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1006,18 +1006,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>441</v>
+        <v>457</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1068</v>
+        <v>1084</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>21360</v>
+        <v>21680</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1116,18 +1116,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>389</v>
+        <v>425</v>
       </c>
       <c r="O24" s="1">
         <v>20</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="0"/>
-        <v>417</v>
+        <v>453</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>8340</v>
+        <v>9060</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32C2C07-0CA8-41FD-B855-7084746D577B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2567210-5E6A-48B7-98B2-A021134FF006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27570" yWindow="795" windowWidth="16590" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -887,18 +887,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="O14" s="1">
         <v>20</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>2332</v>
+        <v>2328</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>46640</v>
+        <v>46560</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2567210-5E6A-48B7-98B2-A021134FF006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D31AC3-248C-4E9E-B7F5-05EE43EC114F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27570" yWindow="795" windowWidth="16590" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23535" yWindow="630" windowWidth="16590" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -1006,18 +1006,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1084</v>
+        <v>1080</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>21680</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D31AC3-248C-4E9E-B7F5-05EE43EC114F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1903B152-2F19-4910-AC89-7CDF893E5220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23535" yWindow="630" windowWidth="16590" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26070" yWindow="180" windowWidth="23445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -887,18 +887,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>365</v>
+        <v>389</v>
       </c>
       <c r="O14" s="1">
         <v>20</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>2328</v>
+        <v>2352</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>46560</v>
+        <v>47040</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -978,18 +978,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>133</v>
+        <v>161</v>
       </c>
       <c r="O18" s="1">
         <v>20</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>582</v>
+        <v>610</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>11640</v>
+        <v>12200</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1006,18 +1006,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>453</v>
+        <v>477</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1104</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>21600</v>
+        <v>22080</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1116,18 +1116,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>425</v>
+        <v>461</v>
       </c>
       <c r="O24" s="1">
         <v>20</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="0"/>
-        <v>453</v>
+        <v>489</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>9060</v>
+        <v>9780</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1903B152-2F19-4910-AC89-7CDF893E5220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239E7B27-6029-44AB-8E33-3DA7E25D8DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26070" yWindow="180" windowWidth="23445" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>MANO DE OBRA AÑO 2026</t>
   </si>
@@ -157,6 +157,9 @@
   </si>
   <si>
     <t>2600 - OBRA CAMPO</t>
+  </si>
+  <si>
+    <t>26022 - OBRA COLEGIO MONOVAR</t>
   </si>
 </sst>
 </file>
@@ -506,7 +509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q28"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.85546875" customWidth="1"/>
@@ -1188,6 +1191,25 @@
         <v>19055.330000000002</v>
       </c>
     </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>41</v>
+      </c>
+      <c r="J29" s="2">
+        <v>18</v>
+      </c>
+      <c r="O29" s="1">
+        <v>20</v>
+      </c>
+      <c r="P29" s="1">
+        <f t="shared" ref="P29" si="2">SUM(B29:M29)</f>
+        <v>18</v>
+      </c>
+      <c r="Q29" s="1">
+        <f t="shared" ref="Q29" si="3">O29*P29</f>
+        <v>360</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{239E7B27-6029-44AB-8E33-3DA7E25D8DE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AE54F7-FBA9-47EA-9CF7-EB4638695244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -890,18 +890,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>389</v>
+        <v>413</v>
       </c>
       <c r="O14" s="1">
         <v>20</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>2352</v>
+        <v>2376</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>47040</v>
+        <v>47520</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -981,18 +981,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="O18" s="1">
         <v>20</v>
       </c>
       <c r="P18" s="1">
         <f t="shared" si="0"/>
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>12200</v>
+        <v>12840</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1009,18 +1009,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>477</v>
+        <v>509</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1104</v>
+        <v>1136</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>22080</v>
+        <v>22720</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>461</v>
+        <v>493</v>
       </c>
       <c r="O24" s="1">
         <v>20</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="0"/>
-        <v>489</v>
+        <v>521</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>9780</v>
+        <v>10420</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AE54F7-FBA9-47EA-9CF7-EB4638695244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81A0958-8BFD-47A2-BE83-CAA549754DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -890,18 +890,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="O14" s="1">
         <v>20</v>
       </c>
       <c r="P14" s="1">
         <f t="shared" si="0"/>
-        <v>2376</v>
+        <v>2400</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>47520</v>
+        <v>48000</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1009,18 +1009,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>509</v>
+        <v>533</v>
       </c>
       <c r="O19" s="1">
         <v>20</v>
       </c>
       <c r="P19" s="1">
         <f t="shared" si="0"/>
-        <v>1136</v>
+        <v>1160</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>22720</v>
+        <v>23200</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1097,18 +1097,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="O23" s="1">
         <v>20</v>
       </c>
       <c r="P23" s="1">
         <f t="shared" si="0"/>
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>1680</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>493</v>
+        <v>525</v>
       </c>
       <c r="O24" s="1">
         <v>20</v>
       </c>
       <c r="P24" s="1">
         <f t="shared" si="0"/>
-        <v>521</v>
+        <v>553</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>10420</v>
+        <v>11060</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81A0958-8BFD-47A2-BE83-CAA549754DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E294D69-B1B1-4FD7-8C05-933CE314A8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
   <si>
     <t>MANO DE OBRA AÑO 2026</t>
   </si>
@@ -160,6 +160,9 @@
   </si>
   <si>
     <t>26022 - OBRA COLEGIO MONOVAR</t>
+  </si>
+  <si>
+    <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
   </si>
 </sst>
 </file>
@@ -198,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -207,6 +210,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -509,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.85546875" customWidth="1"/>
@@ -586,15 +590,15 @@
         <v>4</v>
       </c>
       <c r="O4" s="1">
-        <v>20</v>
-      </c>
-      <c r="P4" s="1">
-        <f t="shared" ref="P4:P26" si="0">SUM(B4:M4)</f>
+        <v>17</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" ref="P4:P30" si="0">SUM(B4:M4)</f>
         <v>100</v>
       </c>
       <c r="Q4" s="1">
         <f t="shared" ref="Q4:Q26" si="1">O4*P4</f>
-        <v>2000</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -614,15 +618,15 @@
         <v>4</v>
       </c>
       <c r="O5" s="1">
-        <v>20</v>
-      </c>
-      <c r="P5" s="1">
+        <v>17</v>
+      </c>
+      <c r="P5" s="4">
         <f t="shared" si="0"/>
         <v>437</v>
       </c>
       <c r="Q5" s="1">
         <f t="shared" si="1"/>
-        <v>8740</v>
+        <v>7429</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -648,15 +652,15 @@
         <v>16</v>
       </c>
       <c r="O6" s="1">
-        <v>20</v>
-      </c>
-      <c r="P6" s="1">
+        <v>17</v>
+      </c>
+      <c r="P6" s="4">
         <f t="shared" si="0"/>
         <v>440</v>
       </c>
       <c r="Q6" s="1">
         <f t="shared" si="1"/>
-        <v>8800</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
@@ -676,15 +680,15 @@
         <v>16</v>
       </c>
       <c r="O7" s="1">
-        <v>20</v>
-      </c>
-      <c r="P7" s="1">
+        <v>17</v>
+      </c>
+      <c r="P7" s="4">
         <f t="shared" si="0"/>
         <v>643</v>
       </c>
       <c r="Q7" s="1">
         <f t="shared" si="1"/>
-        <v>12860</v>
+        <v>10931</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
@@ -719,15 +723,15 @@
         <v>76</v>
       </c>
       <c r="O8" s="1">
-        <v>20</v>
-      </c>
-      <c r="P8" s="1">
+        <v>17</v>
+      </c>
+      <c r="P8" s="4">
         <f t="shared" si="0"/>
         <v>4119</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="1"/>
-        <v>82380</v>
+        <v>70023</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -747,15 +751,15 @@
         <v>39</v>
       </c>
       <c r="O9" s="1">
-        <v>20</v>
-      </c>
-      <c r="P9" s="1">
+        <v>17</v>
+      </c>
+      <c r="P9" s="4">
         <f t="shared" si="0"/>
         <v>750</v>
       </c>
       <c r="Q9" s="1">
         <f t="shared" si="1"/>
-        <v>15000</v>
+        <v>12750</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -769,15 +773,15 @@
         <v>10</v>
       </c>
       <c r="O10" s="1">
-        <v>20</v>
-      </c>
-      <c r="P10" s="1">
+        <v>17</v>
+      </c>
+      <c r="P10" s="4">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
       <c r="Q10" s="1">
         <f t="shared" si="1"/>
-        <v>1020</v>
+        <v>867</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
@@ -794,15 +798,15 @@
         <v>133</v>
       </c>
       <c r="O11" s="1">
-        <v>20</v>
-      </c>
-      <c r="P11" s="1">
+        <v>17</v>
+      </c>
+      <c r="P11" s="4">
         <f t="shared" si="0"/>
         <v>592</v>
       </c>
       <c r="Q11" s="1">
         <f t="shared" si="1"/>
-        <v>11840</v>
+        <v>10064</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
@@ -828,15 +832,15 @@
         <v>297</v>
       </c>
       <c r="O12" s="1">
-        <v>20</v>
-      </c>
-      <c r="P12" s="1">
+        <v>17</v>
+      </c>
+      <c r="P12" s="4">
         <f t="shared" si="0"/>
         <v>1576</v>
       </c>
       <c r="Q12" s="1">
         <f t="shared" si="1"/>
-        <v>31520</v>
+        <v>26792</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.25">
@@ -853,15 +857,15 @@
         <v>262</v>
       </c>
       <c r="O13" s="1">
-        <v>20</v>
-      </c>
-      <c r="P13" s="1">
+        <v>17</v>
+      </c>
+      <c r="P13" s="4">
         <f t="shared" si="0"/>
         <v>537</v>
       </c>
       <c r="Q13" s="1">
         <f t="shared" si="1"/>
-        <v>10740</v>
+        <v>9129</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.25">
@@ -893,15 +897,15 @@
         <v>437</v>
       </c>
       <c r="O14" s="1">
-        <v>20</v>
-      </c>
-      <c r="P14" s="1">
+        <v>17</v>
+      </c>
+      <c r="P14" s="4">
         <f t="shared" si="0"/>
         <v>2400</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>48000</v>
+        <v>40800</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -912,15 +916,15 @@
         <v>52</v>
       </c>
       <c r="O15" s="1">
-        <v>20</v>
-      </c>
-      <c r="P15" s="1">
+        <v>17</v>
+      </c>
+      <c r="P15" s="4">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
       <c r="Q15" s="1">
         <f t="shared" si="1"/>
-        <v>1040</v>
+        <v>884</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.25">
@@ -931,15 +935,15 @@
         <v>117</v>
       </c>
       <c r="O16" s="1">
-        <v>20</v>
-      </c>
-      <c r="P16" s="1">
+        <v>17</v>
+      </c>
+      <c r="P16" s="4">
         <f t="shared" si="0"/>
         <v>117</v>
       </c>
       <c r="Q16" s="1">
         <f t="shared" si="1"/>
-        <v>2340</v>
+        <v>1989</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -959,15 +963,15 @@
         <v>20</v>
       </c>
       <c r="O17" s="1">
-        <v>20</v>
-      </c>
-      <c r="P17" s="1">
+        <v>17</v>
+      </c>
+      <c r="P17" s="4">
         <f t="shared" si="0"/>
         <v>865</v>
       </c>
       <c r="Q17" s="1">
         <f t="shared" si="1"/>
-        <v>17300</v>
+        <v>14705</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -984,15 +988,15 @@
         <v>193</v>
       </c>
       <c r="O18" s="1">
-        <v>20</v>
-      </c>
-      <c r="P18" s="1">
+        <v>17</v>
+      </c>
+      <c r="P18" s="4">
         <f t="shared" si="0"/>
         <v>642</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>12840</v>
+        <v>10914</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1012,15 +1016,15 @@
         <v>533</v>
       </c>
       <c r="O19" s="1">
-        <v>20</v>
-      </c>
-      <c r="P19" s="1">
+        <v>17</v>
+      </c>
+      <c r="P19" s="4">
         <f t="shared" si="0"/>
         <v>1160</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>23200</v>
+        <v>19720</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1037,15 +1041,15 @@
         <v>60</v>
       </c>
       <c r="O20" s="1">
-        <v>20</v>
-      </c>
-      <c r="P20" s="1">
+        <v>17</v>
+      </c>
+      <c r="P20" s="4">
         <f t="shared" si="0"/>
         <v>304</v>
       </c>
       <c r="Q20" s="1">
         <f t="shared" si="1"/>
-        <v>6080</v>
+        <v>5168</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.25">
@@ -1059,15 +1063,15 @@
         <v>88</v>
       </c>
       <c r="O21" s="1">
-        <v>20</v>
-      </c>
-      <c r="P21" s="1">
+        <v>17</v>
+      </c>
+      <c r="P21" s="4">
         <f t="shared" si="0"/>
         <v>221</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>4420</v>
+        <v>3757</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1081,15 +1085,15 @@
         <v>350</v>
       </c>
       <c r="O22" s="1">
-        <v>20</v>
-      </c>
-      <c r="P22" s="1">
+        <v>17</v>
+      </c>
+      <c r="P22" s="4">
         <f t="shared" si="0"/>
         <v>413</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" si="1"/>
-        <v>8260</v>
+        <v>7021</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1100,15 +1104,15 @@
         <v>116</v>
       </c>
       <c r="O23" s="1">
-        <v>20</v>
-      </c>
-      <c r="P23" s="1">
+        <v>17</v>
+      </c>
+      <c r="P23" s="4">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>2320</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1122,15 +1126,15 @@
         <v>525</v>
       </c>
       <c r="O24" s="1">
-        <v>20</v>
-      </c>
-      <c r="P24" s="1">
+        <v>17</v>
+      </c>
+      <c r="P24" s="4">
         <f t="shared" si="0"/>
         <v>553</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>11060</v>
+        <v>9401</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1141,15 +1145,15 @@
         <v>24</v>
       </c>
       <c r="O25" s="1">
-        <v>20</v>
-      </c>
-      <c r="P25" s="1">
+        <v>17</v>
+      </c>
+      <c r="P25" s="4">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="Q25" s="1">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>408</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.25">
@@ -1160,15 +1164,15 @@
         <v>18</v>
       </c>
       <c r="O26" s="1">
-        <v>20</v>
-      </c>
-      <c r="P26" s="1">
+        <v>17</v>
+      </c>
+      <c r="P26" s="4">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="Q26" s="1">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>306</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.25">
@@ -1176,9 +1180,12 @@
         <v>39</v>
       </c>
       <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
+      <c r="P27" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="Q27" s="1">
-        <v>10550.72</v>
+        <v>8976</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.25">
@@ -1186,9 +1193,12 @@
         <v>40</v>
       </c>
       <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
+      <c r="P28" s="4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="Q28" s="1">
-        <v>19055.330000000002</v>
+        <v>16201</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.25">
@@ -1199,15 +1209,34 @@
         <v>18</v>
       </c>
       <c r="O29" s="1">
+        <v>17</v>
+      </c>
+      <c r="P29" s="4">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="Q29" s="1">
+        <f t="shared" ref="Q29:Q30" si="2">O29*P29</f>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J30" s="2">
         <v>20</v>
       </c>
-      <c r="P29" s="1">
-        <f t="shared" ref="P29" si="2">SUM(B29:M29)</f>
-        <v>18</v>
-      </c>
-      <c r="Q29" s="1">
-        <f t="shared" ref="Q29" si="3">O29*P29</f>
-        <v>360</v>
+      <c r="O30" s="1">
+        <v>17</v>
+      </c>
+      <c r="P30" s="4">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="Q30" s="1">
+        <f t="shared" si="2"/>
+        <v>340</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E294D69-B1B1-4FD7-8C05-933CE314A8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793CE5C3-53AE-4E13-B2E6-90C7268BD6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -894,18 +894,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2400</v>
+        <v>2424</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>40800</v>
+        <v>41208</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>533</v>
+        <v>561</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1188</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>19720</v>
+        <v>20196</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1101,18 +1101,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>1972</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1123,18 +1123,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>525</v>
+        <v>541</v>
       </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>553</v>
+        <v>569</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>9401</v>
+        <v>9673</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1225,18 +1225,18 @@
         <v>42</v>
       </c>
       <c r="J30" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="O30" s="1">
         <v>17</v>
       </c>
       <c r="P30" s="4">
         <f t="shared" si="0"/>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="2"/>
-        <v>340</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793CE5C3-53AE-4E13-B2E6-90C7268BD6F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CF91A2-A144-48DD-B3AA-0B1EB75ED84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -894,18 +894,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>461</v>
+        <v>485</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2424</v>
+        <v>2448</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>41208</v>
+        <v>41616</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>561</v>
+        <v>585</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1188</v>
+        <v>1212</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>20196</v>
+        <v>20604</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1101,18 +1101,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>142</v>
+        <v>174</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>2414</v>
+        <v>2958</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1123,18 +1123,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>541</v>
+        <v>557</v>
       </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>569</v>
+        <v>585</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>9673</v>
+        <v>9945</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">
@@ -1225,18 +1225,18 @@
         <v>42</v>
       </c>
       <c r="J30" s="2">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="O30" s="1">
         <v>17</v>
       </c>
       <c r="P30" s="4">
         <f t="shared" si="0"/>
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="2"/>
-        <v>306</v>
+        <v>612</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25CF91A2-A144-48DD-B3AA-0B1EB75ED84D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2E8A1B-CF73-4F2A-9DC0-1B1FBAF61018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -894,18 +894,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>485</v>
+        <v>513</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2448</v>
+        <v>2476</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>41616</v>
+        <v>42092</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -985,18 +985,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>642</v>
+        <v>666</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>10914</v>
+        <v>11322</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>585</v>
+        <v>613</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1212</v>
+        <v>1240</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>20604</v>
+        <v>21080</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1123,18 +1123,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>557</v>
+        <v>589</v>
       </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>585</v>
+        <v>617</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>9945</v>
+        <v>10489</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D2E8A1B-CF73-4F2A-9DC0-1B1FBAF61018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7201E783-B6DA-4CF3-9960-957B19261BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26130" yWindow="195" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -894,18 +894,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>513</v>
+        <v>549</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2476</v>
+        <v>2512</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>42092</v>
+        <v>42704</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -985,18 +985,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>217</v>
+        <v>241</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>666</v>
+        <v>690</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>11322</v>
+        <v>11730</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1240</v>
+        <v>1260</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>21080</v>
+        <v>21420</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1123,18 +1123,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>10489</v>
+        <v>11033</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7201E783-B6DA-4CF3-9960-957B19261BB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4574EED-84B9-4444-AD5C-900766C72DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26130" yWindow="195" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27195" yWindow="435" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -894,18 +894,18 @@
         <v>370</v>
       </c>
       <c r="J14" s="2">
-        <v>549</v>
+        <v>573</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2512</v>
+        <v>2536</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>42704</v>
+        <v>43112</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -985,18 +985,18 @@
         <v>80</v>
       </c>
       <c r="J18" s="2">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>690</v>
+        <v>718</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>11730</v>
+        <v>12206</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>633</v>
+        <v>657</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1260</v>
+        <v>1284</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>21420</v>
+        <v>21828</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1101,18 +1101,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>2958</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1123,18 +1123,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>621</v>
+        <v>653</v>
       </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>649</v>
+        <v>681</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>11033</v>
+        <v>11577</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4574EED-84B9-4444-AD5C-900766C72DC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABC7D13-7BC6-4F74-B158-65BD38958199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27195" yWindow="435" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="795" yWindow="390" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -162,7 +162,7 @@
     <t>26022 - OBRA COLEGIO MONOVAR</t>
   </si>
   <si>
-    <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD-CALLE SOROLLA, 13-EL CAMPELLO</t>
+    <t>26013 - ARREGLO PAVIMENTOS COMUNIDAD PROPIETARIOS -CALLE SOROLLA, 13. 03560. EL CAMPELLO</t>
   </si>
 </sst>
 </file>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABC7D13-7BC6-4F74-B158-65BD38958199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A852268-6B09-4178-8CED-FDDA28CDF720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="795" yWindow="390" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>657</v>
+        <v>705</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1284</v>
+        <v>1332</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>21828</v>
+        <v>22644</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1101,18 +1101,18 @@
         <v>35</v>
       </c>
       <c r="J23" s="2">
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>178</v>
+        <v>202</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>3026</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1123,18 +1123,18 @@
         <v>28</v>
       </c>
       <c r="J24" s="2">
-        <v>653</v>
+        <v>677</v>
       </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>681</v>
+        <v>705</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>11577</v>
+        <v>11985</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A852268-6B09-4178-8CED-FDDA28CDF720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4AC84B-0472-47FE-8A5A-90FA2A6B71A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25920" yWindow="60" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -1013,18 +1013,18 @@
         <v>237</v>
       </c>
       <c r="J19" s="2">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1332</v>
+        <v>1324</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>22644</v>
+        <v>22508</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1225,18 +1225,18 @@
         <v>42</v>
       </c>
       <c r="J30" s="2">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="O30" s="1">
         <v>17</v>
       </c>
       <c r="P30" s="4">
         <f t="shared" si="0"/>
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q30" s="1">
         <f t="shared" si="2"/>
-        <v>612</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F4AC84B-0472-47FE-8A5A-90FA2A6B71A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10B1BA0-249E-4854-A0E9-88C45C646B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25920" yWindow="60" windowWidth="25335" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -896,16 +896,19 @@
       <c r="J14" s="2">
         <v>573</v>
       </c>
+      <c r="K14" s="2">
+        <v>28</v>
+      </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2536</v>
+        <v>2564</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>43112</v>
+        <v>43588</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1015,16 +1018,19 @@
       <c r="J19" s="2">
         <v>697</v>
       </c>
+      <c r="K19" s="2">
+        <v>28</v>
+      </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1324</v>
+        <v>1352</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>22508</v>
+        <v>22984</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1103,16 +1109,19 @@
       <c r="J23" s="2">
         <v>202</v>
       </c>
+      <c r="K23" s="2">
+        <v>16</v>
+      </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>3434</v>
+        <v>3706</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1125,16 +1134,19 @@
       <c r="J24" s="2">
         <v>677</v>
       </c>
+      <c r="K24" s="2">
+        <v>24</v>
+      </c>
       <c r="O24" s="1">
         <v>17</v>
       </c>
       <c r="P24" s="4">
         <f t="shared" si="0"/>
-        <v>705</v>
+        <v>729</v>
       </c>
       <c r="Q24" s="1">
         <f t="shared" si="1"/>
-        <v>11985</v>
+        <v>12393</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B10B1BA0-249E-4854-A0E9-88C45C646B02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC24CB7E-0344-4915-824D-306597B3D06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2564</v>
+        <v>2588</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>43588</v>
+        <v>43996</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -990,16 +990,19 @@
       <c r="J18" s="2">
         <v>269</v>
       </c>
+      <c r="K18" s="2">
+        <v>28</v>
+      </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>718</v>
+        <v>746</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>12206</v>
+        <v>12682</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1019,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1352</v>
+        <v>1376</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>22984</v>
+        <v>23392</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1110,18 +1113,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>218</v>
+        <v>246</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>3706</v>
+        <v>4182</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC24CB7E-0344-4915-824D-306597B3D06D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B26FD7-7D08-42D3-AF70-D072EEA16FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2588</v>
+        <v>2612</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>43996</v>
+        <v>44404</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1376</v>
+        <v>1400</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>23392</v>
+        <v>23800</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1071,16 +1071,19 @@
       <c r="H21" s="2">
         <v>88</v>
       </c>
+      <c r="K21" s="2">
+        <v>36</v>
+      </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>221</v>
+        <v>257</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>3757</v>
+        <v>4369</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1113,18 +1116,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>246</v>
+        <v>274</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>4182</v>
+        <v>4658</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5B26FD7-7D08-42D3-AF70-D072EEA16FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20E0517-01BE-49AE-9C2D-1E13CA542922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>4369</v>
+        <v>4284</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1096,16 +1096,19 @@
       <c r="I22" s="2">
         <v>350</v>
       </c>
+      <c r="K22" s="2">
+        <v>3</v>
+      </c>
       <c r="O22" s="1">
         <v>17</v>
       </c>
       <c r="P22" s="4">
         <f t="shared" si="0"/>
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="Q22" s="1">
         <f t="shared" si="1"/>
-        <v>7021</v>
+        <v>7072</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20E0517-01BE-49AE-9C2D-1E13CA542922}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA18872-5472-47C9-8803-D21F5FC4E40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2612</v>
+        <v>2640</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>44404</v>
+        <v>44880</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>76</v>
+        <v>104</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1400</v>
+        <v>1428</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>23800</v>
+        <v>24276</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>252</v>
+        <v>284</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>4284</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>274</v>
+        <v>298</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>4658</v>
+        <v>5066</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA18872-5472-47C9-8803-D21F5FC4E40B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3124CC-0515-4B30-8316-86A9DE3FC7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26040" yWindow="1050" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>5066</v>
+        <v>5117</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3124CC-0515-4B30-8316-86A9DE3FC7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A886EB-5B64-4337-AD8A-2171CF2E82A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26040" yWindow="1050" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2640</v>
+        <v>2664</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>44880</v>
+        <v>45288</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1428</v>
+        <v>1452</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>24276</v>
+        <v>24684</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>284</v>
+        <v>316</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>4828</v>
+        <v>5372</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>99</v>
+        <v>131</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>301</v>
+        <v>333</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>5117</v>
+        <v>5661</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A886EB-5B64-4337-AD8A-2171CF2E82A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1C1239-B1A8-4CF0-AE81-A58887A1CCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26040" yWindow="1050" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>128</v>
+        <v>152</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2664</v>
+        <v>2688</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>45288</v>
+        <v>45696</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1452</v>
+        <v>1428</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>24684</v>
+        <v>24276</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE1C1239-B1A8-4CF0-AE81-A58887A1CCB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40807701-6AF3-4090-8444-C9E48D93BED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26040" yWindow="1050" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>152</v>
+        <v>200</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2688</v>
+        <v>2736</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>45696</v>
+        <v>46512</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>5372</v>
+        <v>6052</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>131</v>
+        <v>158</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>5661</v>
+        <v>6120</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40807701-6AF3-4090-8444-C9E48D93BED0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15495F22-5C10-4F48-948F-BD5A52EEFDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>200</v>
+        <v>252</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2736</v>
+        <v>2788</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>46512</v>
+        <v>47396</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>746</v>
+        <v>782</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>12682</v>
+        <v>13294</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1428</v>
+        <v>1434</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>24276</v>
+        <v>24378</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>6052</v>
+        <v>6664</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15495F22-5C10-4F48-948F-BD5A52EEFDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEC5ED2-CB23-4E9B-B3E8-E54B12EF9CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27240" yWindow="645" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>47396</v>
+        <v>47362</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAEC5ED2-CB23-4E9B-B3E8-E54B12EF9CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1910F3D4-938D-4489-BE62-8C77457E4C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27240" yWindow="645" windowWidth="24480" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>250</v>
+        <v>282</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2786</v>
+        <v>2818</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>47362</v>
+        <v>47906</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>110</v>
+        <v>126</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1434</v>
+        <v>1450</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>24378</v>
+        <v>24650</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>171</v>
+        <v>207</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>392</v>
+        <v>428</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>6664</v>
+        <v>7276</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>158</v>
+        <v>202</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>360</v>
+        <v>404</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>6120</v>
+        <v>6868</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1910F3D4-938D-4489-BE62-8C77457E4C8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129B511C-F7D6-4089-B414-D6A613A642C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>282</v>
+        <v>318</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2818</v>
+        <v>2854</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>47906</v>
+        <v>48518</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1450</v>
+        <v>1466</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>24650</v>
+        <v>24922</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>207</v>
+        <v>239</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>428</v>
+        <v>460</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>7276</v>
+        <v>7820</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>202</v>
+        <v>238</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>404</v>
+        <v>440</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>6868</v>
+        <v>7480</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{129B511C-F7D6-4089-B414-D6A613A642C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED1CEE3-F4A3-46B9-B757-CDDE80EA4BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>318</v>
+        <v>354</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2854</v>
+        <v>2890</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>48518</v>
+        <v>49130</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>782</v>
+        <v>801</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>13294</v>
+        <v>13617</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1022,18 +1022,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1466</v>
+        <v>1482</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>24922</v>
+        <v>25194</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>460</v>
+        <v>482</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>7820</v>
+        <v>8194</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>7480</v>
+        <v>7939</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ED1CEE3-F4A3-46B9-B757-CDDE80EA4BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BFFDA0-AF19-4632-AB18-470941A6F67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>354</v>
+        <v>402</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2890</v>
+        <v>2938</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>49130</v>
+        <v>49946</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>801</v>
+        <v>820</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>13617</v>
+        <v>13940</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>482</v>
+        <v>501</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>8194</v>
+        <v>8517</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>265</v>
+        <v>291</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>467</v>
+        <v>493</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>7939</v>
+        <v>8381</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BFFDA0-AF19-4632-AB18-470941A6F67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B37951-AC3D-4EA9-B5C0-30252E5F8D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>402</v>
+        <v>458</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2938</v>
+        <v>2994</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>49946</v>
+        <v>50898</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>839</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>13940</v>
+        <v>14263</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>8517</v>
+        <v>8823</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>493</v>
+        <v>520</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>8381</v>
+        <v>8840</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95B37951-AC3D-4EA9-B5C0-30252E5F8D3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B88589-8821-44B0-B9E3-9BCF40CE014F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>458</v>
+        <v>538</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>2994</v>
+        <v>3074</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>50898</v>
+        <v>52258</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>839</v>
+        <v>855</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>14263</v>
+        <v>14535</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>519</v>
+        <v>535</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>8823</v>
+        <v>9095</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>318</v>
+        <v>350</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>520</v>
+        <v>552</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>8840</v>
+        <v>9384</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B88589-8821-44B0-B9E3-9BCF40CE014F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD1D065-069F-49D1-BB34-C28DD6A9110A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-27435" yWindow="675" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3074</v>
+        <v>3080</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>52258</v>
+        <v>52360</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CD1D065-069F-49D1-BB34-C28DD6A9110A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ED5F4B-BB41-42C9-B89B-D0FC82AEDB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-27435" yWindow="675" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>544</v>
+        <v>619</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3080</v>
+        <v>3155</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>52360</v>
+        <v>53635</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>855</v>
+        <v>871</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>14535</v>
+        <v>14807</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>535</v>
+        <v>551</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>9095</v>
+        <v>9367</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>350</v>
+        <v>374</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>9384</v>
+        <v>9792</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1ED5F4B-BB41-42C9-B89B-D0FC82AEDB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B38DD8-41BB-43C7-A9E4-D552AA5625F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -897,18 +897,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>619</v>
+        <v>697</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3155</v>
+        <v>3233</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>53635</v>
+        <v>54961</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -991,18 +991,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>153</v>
+        <v>176</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>871</v>
+        <v>894</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>14807</v>
+        <v>15198</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1072,18 +1072,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>551</v>
+        <v>569</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>9367</v>
+        <v>9673</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1119,18 +1119,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>374</v>
+        <v>393</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>576</v>
+        <v>595</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>9792</v>
+        <v>10115</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B38DD8-41BB-43C7-A9E4-D552AA5625F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E9D02D-C2E6-4845-A1B6-5B65C4AE4336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26430" yWindow="495" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -679,16 +679,19 @@
       <c r="F7" s="2">
         <v>16</v>
       </c>
+      <c r="K7" s="2">
+        <v>4</v>
+      </c>
       <c r="O7" s="1">
         <v>17</v>
       </c>
       <c r="P7" s="4">
         <f t="shared" si="0"/>
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="Q7" s="1">
         <f t="shared" si="1"/>
-        <v>10931</v>
+        <v>10999</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26E9D02D-C2E6-4845-A1B6-5B65C4AE4336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE34646-2FF4-4700-A193-6D4F33C97D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-26430" yWindow="495" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -900,18 +900,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3233</v>
+        <v>3238</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>54961</v>
+        <v>55046</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAE34646-2FF4-4700-A193-6D4F33C97D5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE7CF4D-8229-46F2-820E-AF0F995FFEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26430" yWindow="495" windowWidth="25980" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -725,16 +725,19 @@
       <c r="J8" s="2">
         <v>76</v>
       </c>
+      <c r="K8" s="2">
+        <v>16</v>
+      </c>
       <c r="O8" s="1">
         <v>17</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="0"/>
-        <v>4119</v>
+        <v>4135</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="1"/>
-        <v>70023</v>
+        <v>70295</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -900,18 +903,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>702</v>
+        <v>769</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3238</v>
+        <v>3305</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>55046</v>
+        <v>56185</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -1075,18 +1078,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>348</v>
+        <v>372</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>9673</v>
+        <v>10081</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1122,18 +1125,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>393</v>
+        <v>425</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>595</v>
+        <v>627</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>10115</v>
+        <v>10659</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAE7CF4D-8229-46F2-820E-AF0F995FFEEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC7F471-A37F-4687-9348-AF5E9702CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -726,18 +726,18 @@
         <v>76</v>
       </c>
       <c r="K8" s="2">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O8" s="1">
         <v>17</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="0"/>
-        <v>4135</v>
+        <v>4143</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="1"/>
-        <v>70295</v>
+        <v>70431</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -903,18 +903,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>769</v>
+        <v>839</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3305</v>
+        <v>3375</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>56185</v>
+        <v>57375</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -997,18 +997,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>15198</v>
+        <v>15334</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1078,18 +1078,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>593</v>
+        <v>620</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>10081</v>
+        <v>10540</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1125,18 +1125,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>425</v>
+        <v>467</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>627</v>
+        <v>669</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>10659</v>
+        <v>11373</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCC7F471-A37F-4687-9348-AF5E9702CBE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E7272-E4A9-4F00-9F5B-999DEBCC80BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-26760" yWindow="360" windowWidth="21420" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4E7272-E4A9-4F00-9F5B-999DEBCC80BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FB3488-6B4B-4F1A-8449-21F4B1982AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26760" yWindow="360" windowWidth="21420" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -903,18 +903,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3375</v>
+        <v>3374</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>57375</v>
+        <v>57358</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4FB3488-6B4B-4F1A-8449-21F4B1982AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9802AF8-2644-4EE7-A17C-85C47C51391C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -903,18 +903,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>838</v>
+        <v>893</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3374</v>
+        <v>3429</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>57358</v>
+        <v>58293</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -997,18 +997,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>902</v>
+        <v>918</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>15334</v>
+        <v>15606</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1028,18 +1028,18 @@
         <v>697</v>
       </c>
       <c r="K19" s="2">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="O19" s="1">
         <v>17</v>
       </c>
       <c r="P19" s="4">
         <f t="shared" si="0"/>
-        <v>1482</v>
+        <v>1506</v>
       </c>
       <c r="Q19" s="1">
         <f t="shared" si="1"/>
-        <v>25194</v>
+        <v>25602</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
@@ -1078,18 +1078,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>399</v>
+        <v>419</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>620</v>
+        <v>640</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>10540</v>
+        <v>10880</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1125,18 +1125,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>467</v>
+        <v>491</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>669</v>
+        <v>693</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>11373</v>
+        <v>11781</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">

--- a/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
+++ b/dashboard/GASTOS MANO DE OBRA POR MESES 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jjmax\Downloads\1\dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9802AF8-2644-4EE7-A17C-85C47C51391C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493CEC04-D49C-4670-9A2D-A9696B015CF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-25710" yWindow="0" windowWidth="21420" windowHeight="14190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mano de Obra" sheetId="1" r:id="rId1"/>
@@ -726,18 +726,18 @@
         <v>76</v>
       </c>
       <c r="K8" s="2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="O8" s="1">
         <v>17</v>
       </c>
       <c r="P8" s="4">
         <f t="shared" si="0"/>
-        <v>4143</v>
+        <v>4149</v>
       </c>
       <c r="Q8" s="1">
         <f t="shared" si="1"/>
-        <v>70431</v>
+        <v>70533</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -903,18 +903,18 @@
         <v>573</v>
       </c>
       <c r="K14" s="2">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="O14" s="1">
         <v>17</v>
       </c>
       <c r="P14" s="4">
         <f t="shared" si="0"/>
-        <v>3429</v>
+        <v>3504</v>
       </c>
       <c r="Q14" s="1">
         <f t="shared" si="1"/>
-        <v>58293</v>
+        <v>59568</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.25">
@@ -997,18 +997,18 @@
         <v>269</v>
       </c>
       <c r="K18" s="2">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="O18" s="1">
         <v>17</v>
       </c>
       <c r="P18" s="4">
         <f t="shared" si="0"/>
-        <v>918</v>
+        <v>928</v>
       </c>
       <c r="Q18" s="1">
         <f t="shared" si="1"/>
-        <v>15606</v>
+        <v>15776</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
@@ -1078,18 +1078,18 @@
         <v>88</v>
       </c>
       <c r="K21" s="2">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="O21" s="1">
         <v>17</v>
       </c>
       <c r="P21" s="4">
         <f t="shared" si="0"/>
-        <v>640</v>
+        <v>664</v>
       </c>
       <c r="Q21" s="1">
         <f t="shared" si="1"/>
-        <v>10880</v>
+        <v>11288</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1125,18 +1125,18 @@
         <v>202</v>
       </c>
       <c r="K23" s="2">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="O23" s="1">
         <v>17</v>
       </c>
       <c r="P23" s="4">
         <f t="shared" si="0"/>
-        <v>693</v>
+        <v>717</v>
       </c>
       <c r="Q23" s="1">
         <f t="shared" si="1"/>
-        <v>11781</v>
+        <v>12189</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
